--- a/YCSB/ycsb_20251114_132918/vmstat_summary.xlsx
+++ b/YCSB/ycsb_20251114_132918/vmstat_summary.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="vmstat_diff" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="cpu_bound" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="io_bound" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="mem_bound" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +533,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10w_cpu_bound</t>
+          <t>10w</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -601,47 +603,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10w_io_bound</t>
+          <t>cpu</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3413713</v>
+        <v>3324261</v>
       </c>
       <c r="C3" t="n">
-        <v>677</v>
+        <v>262</v>
       </c>
       <c r="D3" t="n">
-        <v>33258</v>
+        <v>24784</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>110344</v>
+        <v>52884</v>
       </c>
       <c r="G3" t="n">
-        <v>29796080</v>
+        <v>21298448</v>
       </c>
       <c r="H3" t="n">
-        <v>21305033</v>
+        <v>16162106</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>14295200</v>
+        <v>10668109</v>
       </c>
       <c r="K3" t="n">
-        <v>7009534</v>
+        <v>5491457</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>7542389</v>
+        <v>5567541</v>
       </c>
       <c r="N3" t="n">
-        <v>7443730</v>
+        <v>5320505</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -662,56 +664,56 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>112992256</v>
+        <v>54153216</v>
       </c>
       <c r="V3" t="n">
-        <v>30511185920</v>
+        <v>21809610752</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10w_mem_bound</t>
+          <t>rr</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1026989</v>
+        <v>5383767</v>
       </c>
       <c r="C4" t="n">
-        <v>260</v>
+        <v>1473</v>
       </c>
       <c r="D4" t="n">
-        <v>-94</v>
+        <v>50636</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>52476</v>
+        <v>56200</v>
       </c>
       <c r="G4" t="n">
-        <v>3293824</v>
+        <v>26605096</v>
       </c>
       <c r="H4" t="n">
-        <v>2965929</v>
+        <v>18785525</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2230470</v>
+        <v>11398100</v>
       </c>
       <c r="K4" t="n">
-        <v>735459</v>
+        <v>7386338</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>844870</v>
+        <v>6761988</v>
       </c>
       <c r="N4" t="n">
-        <v>822793</v>
+        <v>6643893</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -732,56 +734,56 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>53735424</v>
+        <v>57548800</v>
       </c>
       <c r="V4" t="n">
-        <v>3372875776</v>
+        <v>27243618304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cpu_cpu_bound</t>
+          <t>thr</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3324261</v>
+        <v>5622637</v>
       </c>
       <c r="C5" t="n">
-        <v>262</v>
+        <v>1489</v>
       </c>
       <c r="D5" t="n">
-        <v>24784</v>
+        <v>33718</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>52884</v>
+        <v>56072</v>
       </c>
       <c r="G5" t="n">
-        <v>21298448</v>
+        <v>26759744</v>
       </c>
       <c r="H5" t="n">
-        <v>16162106</v>
+        <v>18686838</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10668109</v>
+        <v>9749123</v>
       </c>
       <c r="K5" t="n">
-        <v>5491457</v>
+        <v>8934704</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5567541</v>
+        <v>6772926</v>
       </c>
       <c r="N5" t="n">
-        <v>5320505</v>
+        <v>6682440</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -802,569 +804,821 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>54153216</v>
+        <v>57417728</v>
       </c>
       <c r="V5" t="n">
-        <v>21809610752</v>
+        <v>27401977856</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cpu_io_bound</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pgfault</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pgmajfault</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>nr_dirty</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>nr_writeback</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pgpgin</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pgpgout</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>numa_hit</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>numa_miss</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>numa_local</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>numa_other</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>numa_interleave</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>nr_dirtied</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>nr_written</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>pswpin</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>pswpout</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>allocstall_dma</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>allocstall_dma32</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>allocstall_normal</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>allocstall_movable</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>pgpgin_bytes</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>pgpgout_bytes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10w</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3413713</v>
+      </c>
+      <c r="C2" t="n">
+        <v>677</v>
+      </c>
+      <c r="D2" t="n">
+        <v>33258</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>110344</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29796080</v>
+      </c>
+      <c r="H2" t="n">
+        <v>21305033</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14295200</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7009534</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7542389</v>
+      </c>
+      <c r="N2" t="n">
+        <v>7443730</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>112992256</v>
+      </c>
+      <c r="V2" t="n">
+        <v>30511185920</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>4168058</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C3" t="n">
         <v>678</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D3" t="n">
         <v>33568</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>110132</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G3" t="n">
         <v>29007936</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H3" t="n">
         <v>21091242</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>12072906</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K3" t="n">
         <v>9018336</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>7487361</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N3" t="n">
         <v>7247325</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
         <v>112775168</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V3" t="n">
         <v>29704126464</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cpu_mem_bound</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>rr</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6050237</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2192</v>
+      </c>
+      <c r="D4" t="n">
+        <v>46782</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>113788</v>
+      </c>
+      <c r="G4" t="n">
+        <v>37709820</v>
+      </c>
+      <c r="H4" t="n">
+        <v>26027170</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12076429</v>
+      </c>
+      <c r="K4" t="n">
+        <v>13947795</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9525656</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9417240</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>116518912</v>
+      </c>
+      <c r="V4" t="n">
+        <v>38614855680</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thr</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6387427</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2193</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50660</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>116184</v>
+      </c>
+      <c r="G5" t="n">
+        <v>37929668</v>
+      </c>
+      <c r="H5" t="n">
+        <v>26148600</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16488432</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9686151</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9584633</v>
+      </c>
+      <c r="N5" t="n">
+        <v>9472047</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>118972416</v>
+      </c>
+      <c r="V5" t="n">
+        <v>38839980032</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pgfault</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pgmajfault</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>nr_dirty</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>nr_writeback</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pgpgin</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pgpgout</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>numa_hit</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>numa_miss</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>numa_local</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>numa_other</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>numa_interleave</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>nr_dirtied</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>nr_written</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>pswpin</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>pswpout</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>allocstall_dma</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>allocstall_dma32</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>allocstall_normal</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>allocstall_movable</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>pgpgin_bytes</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>pgpgout_bytes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10w</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1026989</v>
+      </c>
+      <c r="C2" t="n">
+        <v>260</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-94</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>52476</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3293824</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2965929</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2230470</v>
+      </c>
+      <c r="K2" t="n">
+        <v>735459</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>844870</v>
+      </c>
+      <c r="N2" t="n">
+        <v>822793</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>53735424</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3372875776</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cpu</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>1025584</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C3" t="n">
         <v>260</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D3" t="n">
         <v>-118</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>52512</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G3" t="n">
         <v>3294236</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H3" t="n">
         <v>2988176</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>2210880</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K3" t="n">
         <v>777296</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>844909</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N3" t="n">
         <v>822855</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
         <v>53772288</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V3" t="n">
         <v>3373297664</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>rr_cpu_bound</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5383767</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1473</v>
-      </c>
-      <c r="D8" t="n">
-        <v>50636</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>56200</v>
-      </c>
-      <c r="G8" t="n">
-        <v>26605096</v>
-      </c>
-      <c r="H8" t="n">
-        <v>18785525</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>11398100</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7386338</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6761988</v>
-      </c>
-      <c r="N8" t="n">
-        <v>6643893</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>57548800</v>
-      </c>
-      <c r="V8" t="n">
-        <v>27243618304</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>rr</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1614527</v>
+      </c>
+      <c r="C4" t="n">
+        <v>679</v>
+      </c>
+      <c r="D4" t="n">
+        <v>17463</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>55692</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3910800</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3166293</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2070195</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1096098</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1017745</v>
+      </c>
+      <c r="N4" t="n">
+        <v>976184</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>57028608</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4004659200</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>rr_io_bound</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>6050237</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2192</v>
-      </c>
-      <c r="D9" t="n">
-        <v>46782</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>113788</v>
-      </c>
-      <c r="G9" t="n">
-        <v>37709820</v>
-      </c>
-      <c r="H9" t="n">
-        <v>26027170</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>12076429</v>
-      </c>
-      <c r="K9" t="n">
-        <v>13947795</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>9525656</v>
-      </c>
-      <c r="N9" t="n">
-        <v>9417240</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>116518912</v>
-      </c>
-      <c r="V9" t="n">
-        <v>38614855680</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>rr_mem_bound</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1614527</v>
-      </c>
-      <c r="C10" t="n">
-        <v>679</v>
-      </c>
-      <c r="D10" t="n">
-        <v>17463</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>55692</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3910800</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3166293</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2070195</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1096098</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1017745</v>
-      </c>
-      <c r="N10" t="n">
-        <v>976184</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>57028608</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4004659200</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>thr_cpu_bound</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5622637</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1489</v>
-      </c>
-      <c r="D11" t="n">
-        <v>33718</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>56072</v>
-      </c>
-      <c r="G11" t="n">
-        <v>26759744</v>
-      </c>
-      <c r="H11" t="n">
-        <v>18686838</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>9749123</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8934704</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>6772926</v>
-      </c>
-      <c r="N11" t="n">
-        <v>6682440</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>57417728</v>
-      </c>
-      <c r="V11" t="n">
-        <v>27401977856</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>thr_io_bound</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>6387427</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2193</v>
-      </c>
-      <c r="D12" t="n">
-        <v>50660</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>116184</v>
-      </c>
-      <c r="G12" t="n">
-        <v>37929668</v>
-      </c>
-      <c r="H12" t="n">
-        <v>26148600</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>16488432</v>
-      </c>
-      <c r="K12" t="n">
-        <v>9686151</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>9584633</v>
-      </c>
-      <c r="N12" t="n">
-        <v>9472047</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>118972416</v>
-      </c>
-      <c r="V12" t="n">
-        <v>38839980032</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>thr_mem_bound</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thr</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>1819260</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C5" t="n">
         <v>674</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D5" t="n">
         <v>14546</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>55512</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G5" t="n">
         <v>3933016</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H5" t="n">
         <v>3166886</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>2180782</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K5" t="n">
         <v>986104</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1020369</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N5" t="n">
         <v>981724</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>56844288</v>
       </c>
-      <c r="V13" t="n">
+      <c r="V5" t="n">
         <v>4027408384</v>
       </c>
     </row>
